--- a/data/trans_dic/P25C$pormicuenta_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,0; 93,68</t>
+          <t>80,86; 93,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,44; 92,57</t>
+          <t>79,03; 92,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,19; 92,31</t>
+          <t>82,32; 91,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,02; 96,21</t>
+          <t>84,73; 96,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,53; 96,5</t>
+          <t>86,0; 96,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,97; 95,15</t>
+          <t>87,07; 94,97</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,65; 99,71</t>
+          <t>89,58; 99,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,98; 98,15</t>
+          <t>77,53; 98,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,77; 99,87</t>
+          <t>89,81; 99,53</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,78; 92,67</t>
+          <t>83,77; 92,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,03; 94,81</t>
+          <t>83,26; 94,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,52; 92,5</t>
+          <t>85,45; 92,56</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,07; 94,14</t>
+          <t>80,28; 94,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,11; 91,59</t>
+          <t>79,17; 91,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,09; 91,84</t>
+          <t>81,94; 91,36</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,04; 100,0</t>
+          <t>26,06; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,81; 100,0</t>
+          <t>89,52; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,4; 98,44</t>
+          <t>83,96; 98,42</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,43; 96,57</t>
+          <t>88,59; 97,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,76; 92,22</t>
+          <t>87,19; 92,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,98; 95,97</t>
+          <t>88,92; 95,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue sin ayuda específica</t>
+          <t>Población cuyo método para dejar de fumar fue sin ayuda específica (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99941; 115582</t>
+          <t>99768; 115455</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51008; 60202</t>
+          <t>51392; 60221</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154846; 173911</t>
+          <t>155097; 173157</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79313; 89751</t>
+          <t>79045; 89629</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47949; 54734</t>
+          <t>48777; 54830</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130466; 142736</t>
+          <t>130610; 142462</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>304372; 338542</t>
+          <t>304136; 338365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17224; 21405</t>
+          <t>16907; 21404</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324356; 360869</t>
+          <t>324519; 359646</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>158583; 175408</t>
+          <t>158549; 175416</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66366; 74877</t>
+          <t>65757; 74683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229415; 248126</t>
+          <t>229215; 248299</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>71408; 82919</t>
+          <t>70709; 82957</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55469; 64221</t>
+          <t>55509; 64486</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129858; 145281</t>
+          <t>129633; 144523</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2026; 6978</t>
+          <t>1818; 6978</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33459; 37254</t>
+          <t>33350; 37254</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37332; 43540</t>
+          <t>37139; 43532</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>743272; 811680</t>
+          <t>744622; 815747</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>286226; 304251</t>
+          <t>287663; 304498</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1041484; 1123271</t>
+          <t>1040795; 1121588</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$pormicuenta_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25C$pormicuenta_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,86; 93,58</t>
+          <t>80,8; 93,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,03; 92,6</t>
+          <t>79,41; 92,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,32; 91,91</t>
+          <t>82,02; 91,94</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,73; 96,08</t>
+          <t>85,02; 96,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,0; 96,67</t>
+          <t>84,39; 96,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,07; 94,97</t>
+          <t>86,6; 95,06</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,58; 99,66</t>
+          <t>84,04; 95,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,53; 98,15</t>
+          <t>78,0; 98,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,81; 99,53</t>
+          <t>85,51; 95,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,77; 92,68</t>
+          <t>83,79; 92,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,26; 94,56</t>
+          <t>83,62; 94,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,45; 92,56</t>
+          <t>85,3; 92,23</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>80,28; 94,18</t>
+          <t>80,6; 93,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,17; 91,97</t>
+          <t>79,71; 92,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,94; 91,36</t>
+          <t>83,08; 91,93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,06; 100,0</t>
+          <t>28,52; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,52; 100,0</t>
+          <t>89,42; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,96; 98,42</t>
+          <t>84,48; 98,0</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>88,59; 97,05</t>
+          <t>86,72; 91,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87,19; 92,3</t>
+          <t>87,44; 92,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,92; 95,83</t>
+          <t>87,71; 91,29</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>109043</t>
+          <t>115260</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165624</t>
+          <t>175960</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99768; 115455</t>
+          <t>105544; 122204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51392; 60221</t>
+          <t>55128; 64203</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155097; 173157</t>
+          <t>164074; 183914</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85489</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52413</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>151069</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79045; 89629</t>
+          <t>87016; 98467</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48777; 54830</t>
+          <t>53028; 60357</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>130610; 142462</t>
+          <t>143046; 157027</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>330904</t>
+          <t>95335</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>350968</t>
+          <t>116141</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>304136; 338365</t>
+          <t>88237; 100127</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16907; 21404</t>
+          <t>17692; 22269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>324519; 359646</t>
+          <t>109173; 121423</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>168621</t>
+          <t>187819</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71141</t>
+          <t>76595</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239763</t>
+          <t>264414</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>158549; 175416</t>
+          <t>176725; 196136</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65757; 74683</t>
+          <t>71166; 80405</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>229215; 248299</t>
+          <t>252511; 273021</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>78110</t>
+          <t>83808</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>69628</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138466</t>
+          <t>153436</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70709; 82957</t>
+          <t>75956; 88458</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55509; 64486</t>
+          <t>63619; 73811</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129633; 144523</t>
+          <t>144607; 160013</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>42225</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1818; 6978</t>
+          <t>1901; 6666</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33350; 37254</t>
+          <t>34129; 38167</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37139; 43532</t>
+          <t>37875; 43936</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>777628</t>
+          <t>580899</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>296659</t>
+          <t>322348</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1074286</t>
+          <t>903245</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>744622; 815747</t>
+          <t>563490; 594593</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>287663; 304498</t>
+          <t>313049; 331014</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1040795; 1121588</t>
+          <t>883937; 920037</t>
         </is>
       </c>
     </row>
